--- a/src/main/resources/rules/puntuation_rules.xlsx
+++ b/src/main/resources/rules/puntuation_rules.xlsx
@@ -504,16 +504,11 @@
           <t>ceu.biolab.cmm.rulePuntuation.dto.RulePuntuationRequestDTO</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ceu.biolab.cmm.shared.dto.FeatureAnnotation.ResultItem</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RuleTable LipidsRetentionTimeRules</t>
+          <t>RuleTable PuntuationByCount</t>
         </is>
       </c>
     </row>
@@ -537,36 +532,26 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>$req : RulePuntuationRequestDTO( $feature : feature )</t>
+          <t>$req : RulePuntuationRequestDTO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>exists( ResultItem( mzValue == $mz ) from $feature.items )</t>
+          <t>feature != null, feature.items != null, feature.items.size() &gt;= 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$req.setScore($score);</t>
+          <t>$req.setScore(1.0);</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rule_1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.0</t>
+          <t>Rule_ge_2</t>
         </is>
       </c>
     </row>
